--- a/medford_monitory_endoskopicheskie.xlsx
+++ b/medford_monitory_endoskopicheskie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Мониторы эндоскопические для оснащения клиник и медицинских учреждений. В каталоге представлено 9 позиций.</t>
+          <t>Мониторы эндоскопические для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_monitory_endoskopicheskie.xlsx
+++ b/medford_monitory_endoskopicheskie.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать мониторы эндоскопические для клиники?</t>
+          <t>Чем эндоскопический монитор отличается от обычного?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Разрешение, пиксели, Активная зона (ГxВ), мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Медицинский эндоскопический монитор отличается точной цветопередачей и контрастом для различения сосудов и тканей, защищённым корпусом, переносящим дезинфекцию, часто влагозащитой и соответствием стандартам электробезопасности операционной. Бытовые мониторы этим требованиям не отвечают и к клиническому применению в стерильной зоне не допускаются.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какую диагональ монитора выбрать?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Диагональ зависит от роли и расстояния до оператора. В линейке доступны 21, 23,8, 24 и 27 дюймов. Основной хирургический монитор обычно берут 27″ (EVORAY S271P, NDS Radiance Ultra), вспомогательный или кабинетный — 21–24″. Ориентируются на комфортное различение мелких структур с рабочего места.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какое разрешение нужно для эндоскопии?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Базовый стандарт категории — Full HD: 1920×1080 или 1920×1200. Формат 1920×1200 (16:10) даёт больше вертикального поля обзора. Разрешение монитора согласуют с выходным сигналом видеопроцессора: если процессор выдаёт Full HD, монитор должен корректно его отображать без потери детализации.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Подойдёт ли монитор к моей стойке?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Совместимость определяется набором видеовходов монитора и выходов видеопроцессора стойки, а также способом крепления. Универсальной совместимости нет: перед заказом сверяют типы разъёмов и то, какой сигнал выдаёт процессор. Крепление (VESA, консоль, подставка) подбирают под конструкцию имеющейся стойки.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Нужен ли монитор с влагозащитой?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Для операционной и зон, где проводится регулярная влажная дезинфекция, влагозащищённый медицинский корпус предпочтителен: он переносит обработку и защищён от попадания жидкости. Для сухого диагностического кабинета требования мягче. Конкретный класс защиты уточняют по паспорту выбранной модели.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что показывает монитор пациента?</t>
+          <t>Можно ли выводить изображение на несколько мониторов?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Одновременный вывод на несколько экранов зависит от видеопроцессора и его выходов, а не только от мониторов. Если нужна дублирующая картинка для ассистента или для записи, эту возможность проверяют на стороне процессора и распределителя сигнала. Мониторы при этом подбирают с совпадающими входами.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Где можно купить монитор пациента?</t>
+          <t>Нужна ли регистрация Росздравнадзора для монитора?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Монитор, применяемый в клинике как часть медицинского оборудования, должен быть зарегистрированным медицинским изделием или входить в состав зарегистрированного комплекса. Статус регистрационного удостоверения уточняют до покупки — это условие законной эксплуатации в лечебном учреждении.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Мониторы эндоскопические для оснащения клиник и медицинских учреждений.</t>
+          <t>Мониторы эндоскопические — специализированные медицинские экраны для вывода видеосигнала с эндоскопических камер в операционной и эндоскопическом кабинете. В категории представлены модели NDS, EVORAY и ОПТИMED с диагоналями от 21 до 27 дюймов. Разрешение линейки — Full HD 1920×1080 и 1920×1200, активная зона экрана от 477×268 мм у NDS EndoVue 21″ до 597,9×336,3 мм у EVORAY S271P 27″. Медицинский корпус рассчитан на дезинфекцию и работу рядом с хирургическим оборудованием.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Эндоскопические мониторы: диагональ и разрешение</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое мониторы эндоскопические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3498,19 +3498,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Эндоскопические мониторы: диагональ и разрешение</t>
         </is>
       </c>
     </row>
@@ -3522,125 +3522,127 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Диагональ</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Разрешение, пиксели</t>
+          <t>Разрешение</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Активная зона (ГxВ), мм</t>
+          <t>Активная зона (Г×В)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Монитор NDS Radiance Ultra 27"</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>NDS EndoVue 21″</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>21″</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1920×1080</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>477×268 мм</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Монитор NDS EndoVue 21 дюйм</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>EVORAY S2421P</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>24″</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>1920×1080</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>477x268</t>
+          <t>518,4×324 мм</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Монитор 24” Full HD эндоскопический-хирургический EVORAY S2421P</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>NDS EndoVue 24″</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>24″</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1920x1080</t>
+          <t>1920×1200</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>518.4х324</t>
+          <t>518×324 мм</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Монитор эндоскопический ОПТИMED 23,8"</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>EVORAY E2421</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>24″</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1920×1200</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>518,4×324 мм</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Монитор эндоскопический ОПТИMED 27"</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>EVORAY S271P</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>27″</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1920×1080</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Монитор 27” Full HD эндоскопический-хирургический EVORAY S271P</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>597.888х336.312</t>
+          <t>597,9×336,3 мм</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3984,12 +3986,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите место установки</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается мониторы эндоскопические: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала уточняют, где монитор будет работать: в стерильной зоне операционной, на эндоскопической стойке или в диагностическом кабинете. От этого зависят требования к корпусу, влагозащите и электробезопасности. Для операционной берут модели в защищённом медицинском исполнении, для кабинета допустимы более простые варианты.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4029,12 +4031,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите диагональ</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Диагональ подбирают по расстоянию до оператора и роли монитора. В линейке — 21, 23,8, 24 и 27 дюймов. Основной хирургический монитор обычно берут крупнее (27″, например EVORAY S271P или NDS Radiance Ultra), вспомогательный или кабинетный — 21–24″. Слишком мелкий экран затрудняет различение мелких структур.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4074,12 +4076,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сверьте разрешение и активную зону</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Разрешение, пиксели, Активная зона (ГxВ), мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Стандарт категории — Full HD: 1920×1080 (EVORAY S2421P) и 1920×1200 (NDS EndoVue 24″, EVORAY E2421). Формат 16:10 (1920×1200) даёт больше вертикального поля. Активная зона у 24″ моделей около 518×324 мм. Разрешение согласуют с выходным сигналом видеопроцессора, чтобы не терять детализацию.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4119,12 +4121,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Проверьте видеовходы</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Монитор соединяют с видеопроцессором стойки, поэтому набор входов (их тип и количество) должен совпадать с его выходами. Заранее уточняют, какие разъёмы использует процессор и нужен ли одновременный вывод на несколько экранов. Несовпадение входов — частая причина, по которой готовый монитор не удаётся подключить.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4164,12 +4166,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Оцените корпус и дезинфекцию</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>В операционной и эндоскопическом кабинете монитор регулярно обрабатывают. Медицинский корпус (например, металлический у ряда моделей) переносит дезинфекцию, защищён от помех и часто имеет влагозащиту. Гладкая передняя панель без глубоких швов упрощает уборку и снижает риск накопления загрязнений.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4209,12 +4211,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните крепление и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Заранее согласуют способ крепления — VESA-кронштейн на стойку, потолочную консоль или настольную подставку — и совместимость с имеющимся оборудованием. Отдельно уточняют условия гарантии, доступность запчастей и подменного фонда, чтобы выход монитора из строя не остановил операционный день.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4264,7 +4266,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Мониторы эндоскопические подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на разрешение, активная зона (гxв), а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Эндоскопический монитор выбирают под конкретную стойку, а не отдельно. Важны не только диагональ и разрешение, но и набор видеовходов: они должны совпадать с выходами видеопроцессора, иначе изображение не выведется в нужном качестве. Для операционной корпус должен переносить регулярную дезинфекцию и соответствовать требованиям электробезопасности — это не опция, а условие допуска в чистую зону.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4548,13 +4550,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое мониторы эндоскопические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Мониторы эндоскопические — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>Эндоскопический монитор — медицинский экран для отображения изображения с эндоскопической камеры во время операций и диагностики. От бытового монитора его отличают точная цветопередача для различения сосудов и тканей, защищённый и легко дезинфицируемый корпус и соответствие стандартам электробезопасности операционной. При выборе сверяют диагональ (в линейке от 21 до 27 дюймов), разрешение (Full HD 1920×1080 или 1920×1200), активную зону экрана, набор видеовходов под видеопроцессор стойки и способ крепления. Монитор подбирают не отдельно, а в связке с видеопроцессором и источником света, проверяя совпадение разъёмов до заказа.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4591,13 +4593,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Эндоскопические мониторы: назначение</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Разрешение, пиксели, Активная зона (ГxВ), мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Эндоскопический монитор выводит изображение с эндоскопических камер во время операций и диагностических процедур — лапароскопии, гастроскопии, колоноскопии. Он входит в состав эндоскопической стойки рядом с видеопроцессором и источником света. Точная цветопередача и контраст помогают хирургу и эндоскописту различать мелкие сосуды, ткани и границы патологических участков.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4634,13 +4636,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Разрешение и размер экрана</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>В категории представлены мониторы с разрешением Full HD 1920×1080 и 1920×1200 и диагоналями 21–27 дюймов. Активная зона 24-дюймовых моделей составляет около 518×324 мм, у 27-дюймового EVORAY S271P — 597,9×336,3 мм. Формат 16:10 даёт дополнительное вертикальное поле, что удобно при работе с вытянутым эндоскопическим кадром.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4677,13 +4679,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Требования к медицинскому корпусу</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Медицинский монитор рассчитан на условия операционной и эндоскопического кабинета: корпус переносит регулярную дезинфекцию, защищён от электромагнитных помех и часто имеет влагозащиту. Соответствие стандартам электробезопасности обязательно для работы в стерильной зоне. Эти свойства отличают специализированный монитор от офисного экрана и определяют допуск в клинику.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4700,6 +4702,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Бренды и совместимость</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В линейке — импортные NDS (EndoVue, Radiance Ultra) и мониторы EVORAY и ОПТИMED с диагоналями 23,8–27″. Выбор модели согласуют с видеопроцессором стойки: набор входов монитора должен совпадать с выходами процессора, а крепление — с конструкцией стойки. Совместимость проверяют до заказа, чтобы монитор корректно отобразил сигнал.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>monitory_endoskopicheskie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
